--- a/data/trans_dic/P41C_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P41C_R-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dificultades para tener un embarazo</t>
+          <t>Población con dificultades para tener un embarazo (tasa de respuesta: 87,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 13,15</t>
+          <t>1,45; 12,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,35</t>
+          <t>0,42; 3,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 6,87</t>
+          <t>1,22; 7,11</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 3,61</t>
+          <t>0,18; 3,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,92; 7,79</t>
+          <t>2,91; 7,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,39</t>
+          <t>0,85; 4,47</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 12,04</t>
+          <t>1,45; 12,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 9,24</t>
+          <t>1,84; 9,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 8,2</t>
+          <t>2,42; 9,17</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 10,05</t>
+          <t>2,54; 10,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,18; 9,36</t>
+          <t>3,14; 9,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 8,27</t>
+          <t>3,45; 8,15</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,04</t>
+          <t>1,15; 5,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,03; 5,73</t>
+          <t>3,08; 5,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,81</t>
+          <t>2,23; 4,79</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dificultades para tener un embarazo</t>
+          <t>Población con dificultades para tener un embarazo (tasa de respuesta: 87,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2337; 19343</t>
+          <t>2128; 17948</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>600; 5319</t>
+          <t>663; 5597</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3896; 21029</t>
+          <t>3717; 21744</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>638; 17777</t>
+          <t>869; 17573</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7183; 19164</t>
+          <t>7151; 18631</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5988; 32376</t>
+          <t>6309; 32958</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1441; 10182</t>
+          <t>1224; 10457</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1896; 10058</t>
+          <t>2008; 10066</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4589; 15859</t>
+          <t>4687; 17727</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3679; 15662</t>
+          <t>3952; 16202</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5766; 16994</t>
+          <t>5703; 16581</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12358; 27884</t>
+          <t>11638; 27490</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10962; 44316</t>
+          <t>10115; 44032</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21071; 39850</t>
+          <t>21409; 40083</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32890; 75740</t>
+          <t>35191; 75386</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P41C_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P41C_R-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 12,2</t>
+          <t>1,68; 14,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,52</t>
+          <t>0,33; 3,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 7,11</t>
+          <t>1,14; 7,75</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 3,57</t>
+          <t>1,04; 5,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,91; 7,57</t>
+          <t>3,07; 8,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,47</t>
+          <t>2,38; 5,4</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 12,37</t>
+          <t>2,27; 12,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 9,25</t>
+          <t>1,41; 8,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 9,17</t>
+          <t>2,42; 8,07</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 10,4</t>
+          <t>2,32; 9,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 9,13</t>
+          <t>2,95; 8,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 8,15</t>
+          <t>3,3; 7,61</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,01</t>
+          <t>2,64; 6,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,08; 5,77</t>
+          <t>2,98; 5,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,79</t>
+          <t>3,19; 5,41</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>7647</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9162</t>
+          <t>9887</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2128; 17948</t>
+          <t>2582; 21653</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>663; 5597</t>
+          <t>557; 5496</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3717; 21744</t>
+          <t>3683; 25029</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6547</t>
+          <t>6527</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12074</t>
+          <t>14042</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18621</t>
+          <t>20570</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>869; 17573</t>
+          <t>2876; 13879</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7151; 18631</t>
+          <t>8348; 22035</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6309; 32958</t>
+          <t>13041; 29612</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>10627</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1224; 10457</t>
+          <t>2180; 12320</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2008; 10066</t>
+          <t>1867; 11067</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4687; 17727</t>
+          <t>5524; 18406</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>8639</t>
+          <t>8734</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>10507</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18942</t>
+          <t>19241</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3952; 16202</t>
+          <t>3946; 16910</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5703; 16581</t>
+          <t>5906; 17265</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11638; 27490</t>
+          <t>12235; 28186</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>26491</t>
+          <t>28556</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>29437</t>
+          <t>31769</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55929</t>
+          <t>60325</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10115; 44032</t>
+          <t>18345; 45806</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21409; 40083</t>
+          <t>23090; 42269</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>35191; 75386</t>
+          <t>46801; 79563</t>
         </is>
       </c>
     </row>
